--- a/scripts/DoAn4_Bemori/test/cases/SCR_DangNhap_NetaBooks.xlsx
+++ b/scripts/DoAn4_Bemori/test/cases/SCR_DangNhap_NetaBooks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Đồ án 4\DoAn4\scripts\DoAn4_Bemori\test\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A451967-3FB6-4539-BC74-1C3EC1CF92EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C39E661-61A1-46F8-820C-6A3AEA160FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,6 +44,12 @@
     <t>https://www.netabooks.vn/</t>
   </si>
   <si>
+    <t>CLICK</t>
+  </si>
+  <si>
+    <t>lnkDangNhap</t>
+  </si>
+  <si>
     <t>INPUT_TEXT</t>
   </si>
   <si>
@@ -59,34 +65,28 @@
     <t>06042004</t>
   </si>
   <si>
+    <t>btnDangNhap</t>
+  </si>
+  <si>
     <t>VERIFY_ELEMENT_VISIBLE</t>
   </si>
   <si>
+    <t>imgDangNhapThanhCong</t>
+  </si>
+  <si>
+    <t>CLOSE_BROWSER</t>
+  </si>
+  <si>
+    <t>VERIFY_ELEMENT_TEXT_EQUALS</t>
+  </si>
+  <si>
     <t>lblDangNhapThatBai</t>
   </si>
   <si>
-    <t>CLOSE_BROWSER</t>
-  </si>
-  <si>
-    <t>VERIFY_ELEMENT_TEXT_EQUALS</t>
-  </si>
-  <si>
     <t>Đăng nhập thất bại. Vui lòng thử lại.</t>
   </si>
   <si>
     <t xml:space="preserve">anhle06042004@gmail.com	</t>
-  </si>
-  <si>
-    <t>imgDangNhapThanhCong</t>
-  </si>
-  <si>
-    <t>CLICK</t>
-  </si>
-  <si>
-    <t>lnkDangNhap</t>
-  </si>
-  <si>
-    <t>btnDangNhap</t>
   </si>
   <si>
     <t>anhle</t>
@@ -438,7 +438,7 @@
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -472,10 +472,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -522,10 +522,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -533,7 +533,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -582,10 +582,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -593,10 +593,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -604,13 +604,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -618,10 +618,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -629,13 +629,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -643,7 +643,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -692,10 +692,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -703,13 +703,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -717,10 +717,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -728,10 +728,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -739,13 +739,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -753,7 +753,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -802,10 +802,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -813,10 +813,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -827,13 +827,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -841,10 +841,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -852,13 +852,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -866,7 +866,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -881,7 +881,7 @@
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
@@ -915,10 +915,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -926,13 +926,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -940,10 +940,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>22</v>
@@ -954,10 +954,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -965,13 +965,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -979,7 +979,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/DoAn4_Bemori/test/cases/SCR_DangNhap_NetaBooks.xlsx
+++ b/scripts/DoAn4_Bemori/test/cases/SCR_DangNhap_NetaBooks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Đồ án 4\DoAn4\scripts\DoAn4_Bemori\test\cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C39E661-61A1-46F8-820C-6A3AEA160FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECD5297-4C6A-4F33-9007-5E4B47D1BFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
